--- a/Result/profitability/1473.xlsx
+++ b/Result/profitability/1473.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35375</v>
+        <v>0.29375</v>
       </c>
       <c r="N2" t="n">
-        <v>16.9475</v>
+        <v>16.88</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.29625</v>
+        <v>0.23875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.98625</v>
+        <v>17.2125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.29625</v>
+        <v>0.14125</v>
       </c>
       <c r="N4" t="n">
-        <v>17.53</v>
+        <v>17.435</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.16875</v>
+        <v>0.2125</v>
       </c>
       <c r="N5" t="n">
-        <v>18.435</v>
+        <v>18.75625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>0.275</v>
+        <v>0.29375</v>
       </c>
       <c r="N6" t="n">
-        <v>19.38875</v>
+        <v>20.16</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0.32125</v>
+        <v>0.3475</v>
       </c>
       <c r="N7" t="n">
-        <v>20.28125</v>
+        <v>20.835</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,13 +1391,13 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3825</v>
+        <v>0.2975</v>
       </c>
       <c r="N8" t="n">
-        <v>21.1025</v>
+        <v>21.07</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1431</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1172</v>
+      </c>
+      <c r="E75" t="n">
+        <v>259</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.27875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.4425</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9855072463768116</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.259999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01414581066376486</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.029411764705882</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1652733118971061</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
